--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK ANTLERLESS DRAW.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026 ELK ANTLERLESS DRAW.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunt Table" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hunt Table'!$A$1:$O$205</definedName>
@@ -861,7 +861,11 @@
           <t>49.2</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -1206,7 +1210,11 @@
           <t>44.5</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -1275,7 +1283,11 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -1344,7 +1356,11 @@
           <t>35.5</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -1413,7 +1429,11 @@
           <t>62.8</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
           <t>7.3</t>
@@ -1482,7 +1502,11 @@
           <t>38.5</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -1620,7 +1644,11 @@
           <t>31.7</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -1689,7 +1717,11 @@
           <t>48.9</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
           <t>5.3</t>
@@ -1896,7 +1928,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr"/>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -1965,7 +2001,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -2034,7 +2074,11 @@
           <t>35.2</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
           <t>6.1</t>
@@ -2172,7 +2216,11 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -2241,7 +2289,11 @@
           <t>71.1</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -2310,7 +2362,11 @@
           <t>50.0</t>
         </is>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -2379,7 +2435,11 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -2448,7 +2508,11 @@
           <t>16.7</t>
         </is>
       </c>
-      <c r="N28" s="3" t="inlineStr"/>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
           <t>6.7</t>
@@ -2517,7 +2581,11 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -2724,7 +2792,11 @@
           <t>63.6</t>
         </is>
       </c>
-      <c r="N32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
           <t>2.8</t>
@@ -2793,7 +2865,11 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="O33" s="5" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -3069,7 +3145,11 @@
           <t>36.8</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -3138,7 +3218,11 @@
           <t>93.3</t>
         </is>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
@@ -3207,7 +3291,11 @@
           <t>77.6</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
           <t>4.1</t>
@@ -3276,7 +3364,11 @@
           <t>39.1</t>
         </is>
       </c>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -3345,7 +3437,11 @@
           <t>51.4</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
           <t>5.6</t>
@@ -3414,7 +3510,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
           <t>2.0</t>
@@ -3483,7 +3583,11 @@
           <t>13.2</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
           <t>9.0</t>
@@ -3552,7 +3656,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -3621,7 +3729,11 @@
           <t>21.7</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -3690,7 +3802,11 @@
           <t>24.4</t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -3759,7 +3875,11 @@
           <t>47.1</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
           <t>6.4</t>
@@ -3828,7 +3948,11 @@
           <t>69.1</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
           <t>5.0</t>
@@ -3966,7 +4090,11 @@
           <t>31.6</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
           <t>8.5</t>
@@ -4035,7 +4163,11 @@
           <t>6.3</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -4104,7 +4236,11 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
@@ -4173,7 +4309,11 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
           <t>7.7</t>
@@ -4242,7 +4382,11 @@
           <t>47.4</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -7611,7 +7755,11 @@
           <t>8.3</t>
         </is>
       </c>
-      <c r="N103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="O103" s="5" t="inlineStr">
         <is>
           <t>8.2</t>
@@ -7680,7 +7828,11 @@
           <t>13.8</t>
         </is>
       </c>
-      <c r="N104" s="3" t="inlineStr"/>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -7887,7 +8039,11 @@
           <t>24.7</t>
         </is>
       </c>
-      <c r="N107" s="5" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O107" s="5" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -8163,7 +8319,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O111" s="5" t="inlineStr">
         <is>
           <t>3.2</t>
@@ -8232,7 +8392,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
@@ -8439,7 +8603,11 @@
           <t>45.9</t>
         </is>
       </c>
-      <c r="N115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="O115" s="5" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -8508,7 +8676,11 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N116" s="3" t="inlineStr"/>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
           <t>14.5</t>
@@ -8577,7 +8749,11 @@
           <t>26.0</t>
         </is>
       </c>
-      <c r="N117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O117" s="5" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -8630,7 +8806,11 @@
         </is>
       </c>
       <c r="M118" s="3" t="inlineStr"/>
-      <c r="N118" s="3" t="inlineStr"/>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O118" s="3" t="inlineStr"/>
     </row>
     <row r="119" ht="28" customHeight="1">
@@ -8752,7 +8932,11 @@
           <t>42.3</t>
         </is>
       </c>
-      <c r="N120" s="3" t="inlineStr"/>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O120" s="3" t="inlineStr">
         <is>
           <t>5.7</t>
@@ -8821,7 +9005,11 @@
           <t>37.9</t>
         </is>
       </c>
-      <c r="N121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O121" s="5" t="inlineStr">
         <is>
           <t>3.5</t>
@@ -8890,7 +9078,11 @@
           <t>57.6</t>
         </is>
       </c>
-      <c r="N122" s="3" t="inlineStr"/>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O122" s="3" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -8959,7 +9151,11 @@
           <t>78.1</t>
         </is>
       </c>
-      <c r="N123" s="5" t="inlineStr"/>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O123" s="5" t="inlineStr">
         <is>
           <t>2.9</t>
@@ -9235,7 +9431,11 @@
           <t>32.5</t>
         </is>
       </c>
-      <c r="N127" s="5" t="inlineStr"/>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
       <c r="O127" s="5" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -9580,7 +9780,11 @@
           <t>8.5</t>
         </is>
       </c>
-      <c r="N132" s="3" t="inlineStr"/>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
           <t>6.2</t>
@@ -9649,7 +9853,11 @@
           <t>34.9</t>
         </is>
       </c>
-      <c r="N133" s="5" t="inlineStr"/>
+      <c r="N133" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O133" s="5" t="inlineStr">
         <is>
           <t>5.1</t>
@@ -9718,7 +9926,11 @@
           <t>47.7</t>
         </is>
       </c>
-      <c r="N134" s="3" t="inlineStr"/>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
           <t>7.5</t>
@@ -9787,7 +9999,11 @@
           <t>25.6</t>
         </is>
       </c>
-      <c r="N135" s="5" t="inlineStr"/>
+      <c r="N135" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O135" s="5" t="inlineStr">
         <is>
           <t>5.9</t>
@@ -9856,7 +10072,11 @@
           <t>40.0</t>
         </is>
       </c>
-      <c r="N136" s="3" t="inlineStr"/>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O136" s="3" t="inlineStr">
         <is>
           <t>6.3</t>
@@ -9925,7 +10145,11 @@
           <t>17.4</t>
         </is>
       </c>
-      <c r="N137" s="5" t="inlineStr"/>
+      <c r="N137" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O137" s="5" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -9994,7 +10218,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="N138" s="3" t="inlineStr"/>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -10063,7 +10291,11 @@
           <t>28.6</t>
         </is>
       </c>
-      <c r="N139" s="5" t="inlineStr"/>
+      <c r="N139" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O139" s="5" t="inlineStr">
         <is>
           <t>6.5</t>
@@ -10132,7 +10364,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N140" s="3" t="inlineStr"/>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
@@ -10388,7 +10624,11 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="3" t="inlineStr"/>
       <c r="M144" s="3" t="inlineStr"/>
-      <c r="N144" s="3" t="inlineStr"/>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O144" s="3" t="inlineStr"/>
     </row>
     <row r="145" ht="28" customHeight="1">
@@ -12435,7 +12675,11 @@
           <t>53.5</t>
         </is>
       </c>
-      <c r="N175" s="5" t="inlineStr"/>
+      <c r="N175" s="5" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
       <c r="O175" s="5" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -12496,7 +12740,11 @@
           <t>46.7</t>
         </is>
       </c>
-      <c r="N176" s="3" t="inlineStr"/>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -12557,7 +12805,11 @@
           <t>55.6</t>
         </is>
       </c>
-      <c r="N177" s="5" t="inlineStr"/>
+      <c r="N177" s="5" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O177" s="5" t="inlineStr">
         <is>
           <t>11.3</t>
@@ -12618,7 +12870,11 @@
           <t>27.8</t>
         </is>
       </c>
-      <c r="N178" s="3" t="inlineStr"/>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
           <t>7.0</t>
@@ -12679,7 +12935,11 @@
           <t>26.2</t>
         </is>
       </c>
-      <c r="N179" s="5" t="inlineStr"/>
+      <c r="N179" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O179" s="5" t="inlineStr">
         <is>
           <t>15.4</t>
@@ -12740,7 +13000,11 @@
           <t>41.6</t>
         </is>
       </c>
-      <c r="N180" s="3" t="inlineStr"/>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="O180" s="3" t="inlineStr">
         <is>
           <t>9.7</t>
@@ -12801,7 +13065,11 @@
           <t>53.1</t>
         </is>
       </c>
-      <c r="N181" s="5" t="inlineStr"/>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O181" s="5" t="inlineStr">
         <is>
           <t>5.4</t>
@@ -12862,7 +13130,11 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="N182" s="3" t="inlineStr"/>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O182" s="3" t="inlineStr">
         <is>
           <t>6.6</t>
@@ -12923,7 +13195,11 @@
           <t>40.9</t>
         </is>
       </c>
-      <c r="N183" s="5" t="inlineStr"/>
+      <c r="N183" s="5" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
       <c r="O183" s="5" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -12984,7 +13260,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="N184" s="3" t="inlineStr"/>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
           <t>9.8</t>
@@ -13045,7 +13325,11 @@
           <t>36.7</t>
         </is>
       </c>
-      <c r="N185" s="5" t="inlineStr"/>
+      <c r="N185" s="5" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
       <c r="O185" s="5" t="inlineStr">
         <is>
           <t>11.4</t>
@@ -13106,7 +13390,11 @@
           <t>60.0</t>
         </is>
       </c>
-      <c r="N186" s="3" t="inlineStr"/>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O186" s="3" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -13167,7 +13455,11 @@
           <t>48.1</t>
         </is>
       </c>
-      <c r="N187" s="5" t="inlineStr"/>
+      <c r="N187" s="5" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
       <c r="O187" s="5" t="inlineStr">
         <is>
           <t>10.1</t>
@@ -13228,7 +13520,11 @@
           <t>30.0</t>
         </is>
       </c>
-      <c r="N188" s="3" t="inlineStr"/>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="O188" s="3" t="inlineStr">
         <is>
           <t>13.7</t>
@@ -13350,7 +13646,11 @@
           <t>21.4</t>
         </is>
       </c>
-      <c r="N190" s="3" t="inlineStr"/>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
       <c r="O190" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
@@ -13533,7 +13833,11 @@
           <t>42.4</t>
         </is>
       </c>
-      <c r="N193" s="5" t="inlineStr"/>
+      <c r="N193" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O193" s="5" t="inlineStr">
         <is>
           <t>5.5</t>
@@ -13594,7 +13898,11 @@
           <t>34.7</t>
         </is>
       </c>
-      <c r="N194" s="3" t="inlineStr"/>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
       <c r="O194" s="3" t="inlineStr">
         <is>
           <t>7.2</t>
@@ -13655,7 +13963,11 @@
           <t>53.7</t>
         </is>
       </c>
-      <c r="N195" s="5" t="inlineStr"/>
+      <c r="N195" s="5" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
       <c r="O195" s="5" t="inlineStr">
         <is>
           <t>4.8</t>
@@ -13862,7 +14174,11 @@
           <t>91.4</t>
         </is>
       </c>
-      <c r="N198" s="3" t="inlineStr"/>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
       <c r="O198" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
@@ -13931,7 +14247,11 @@
           <t>17.8</t>
         </is>
       </c>
-      <c r="N199" s="5" t="inlineStr"/>
+      <c r="N199" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O199" s="5" t="inlineStr">
         <is>
           <t>7.3</t>
@@ -14000,7 +14320,11 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="N200" s="3" t="inlineStr"/>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O200" s="3" t="inlineStr">
         <is>
           <t>5.8</t>
